--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E091264-04B3-4400-954E-0BB545F11C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAA61C5-59F1-4209-AD72-E08B5C9B2DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="2" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="1" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -20601,7 +20601,7 @@
         <v>10.7</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <f t="shared" ref="L9:L11" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
         <v>12</v>
       </c>
       <c r="M9" s="44">

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAA61C5-59F1-4209-AD72-E08B5C9B2DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3BD427-A6A9-4D22-AA22-47D7F7D32963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="1" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="2" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -20544,24 +20544,41 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="P8" s="12">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>6</v>
+      </c>
+      <c r="R8" s="12">
+        <v>72</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
       <c r="T8" s="28">
         <f>SUM(Q8:S8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
+        <v>3.9</v>
+      </c>
+      <c r="U8" s="12">
+        <v>54</v>
+      </c>
+      <c r="V8" s="12">
+        <v>90</v>
+      </c>
+      <c r="W8" s="12">
+        <v>109</v>
+      </c>
       <c r="X8" s="28">
         <f>SUM(U8:W8)/20</f>
-        <v>0</v>
+        <v>12.65</v>
       </c>
       <c r="Y8">
         <f>SUM(P8:S8,U8,V8,W8)/40</f>
-        <v>0</v>
+        <v>9.625</v>
+      </c>
+      <c r="Z8">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.35">
@@ -20614,24 +20631,41 @@
         <f t="shared" ref="O9:O13" si="3">B9</f>
         <v>Salman</v>
       </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="P9" s="12">
+        <v>128</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>44</v>
+      </c>
+      <c r="R9" s="12">
+        <v>34</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
       <c r="T9" s="28">
         <f t="shared" ref="T9:T13" si="4">SUM(Q9:S9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
+        <v>3.9</v>
+      </c>
+      <c r="U9" s="12">
+        <v>55</v>
+      </c>
+      <c r="V9" s="12">
+        <v>45</v>
+      </c>
+      <c r="W9" s="12">
+        <v>56</v>
+      </c>
       <c r="X9" s="28">
         <f t="shared" ref="X9:X13" si="5">SUM(U9:W9)/20</f>
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="Y9:Y13" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="Z9" s="44">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
@@ -20675,29 +20709,48 @@
       <c r="M10" s="44">
         <v>9</v>
       </c>
-      <c r="N10" s="27"/>
+      <c r="N10" s="27">
+        <v>46175</v>
+      </c>
       <c r="O10" s="10" t="str">
         <f t="shared" si="3"/>
         <v>Zesahn</v>
       </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="P10" s="12">
+        <v>70</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>40</v>
+      </c>
+      <c r="R10" s="12">
+        <v>40</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="U10" s="12">
+        <v>60</v>
+      </c>
+      <c r="V10" s="12">
+        <v>80</v>
+      </c>
+      <c r="W10" s="12">
+        <v>60</v>
+      </c>
       <c r="X10" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8.75</v>
+      </c>
+      <c r="Z10" s="44">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
@@ -20743,29 +20796,48 @@
       <c r="M11" s="44">
         <v>10</v>
       </c>
-      <c r="N11" s="11"/>
+      <c r="N11" s="27">
+        <v>46175</v>
+      </c>
       <c r="O11" s="10" t="str">
         <f t="shared" si="3"/>
         <v>Umair</v>
       </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+      <c r="P11" s="12">
+        <v>276</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>39</v>
+      </c>
+      <c r="R11" s="12">
+        <v>40</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
       <c r="T11" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
+        <v>3.95</v>
+      </c>
+      <c r="U11" s="12">
+        <v>80</v>
+      </c>
+      <c r="V11" s="12">
+        <v>40</v>
+      </c>
+      <c r="W11" s="12">
+        <v>40</v>
+      </c>
       <c r="X11" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12.875</v>
+      </c>
+      <c r="Z11" s="44">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
@@ -20797,29 +20869,48 @@
       <c r="M12" s="44">
         <v>10</v>
       </c>
-      <c r="N12" s="11"/>
+      <c r="N12" s="27">
+        <v>46175</v>
+      </c>
       <c r="O12" s="10" t="str">
         <f t="shared" si="3"/>
         <v>Mubeen</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
+      <c r="P12" s="12">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>72</v>
+      </c>
+      <c r="R12" s="12">
+        <v>63</v>
+      </c>
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
       <c r="T12" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
+        <v>6.75</v>
+      </c>
+      <c r="U12" s="12">
+        <v>61</v>
+      </c>
+      <c r="V12" s="12">
+        <v>61</v>
+      </c>
+      <c r="W12" s="12">
+        <v>142</v>
+      </c>
       <c r="X12" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="Y12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11.275</v>
+      </c>
+      <c r="Z12" s="44">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
@@ -20861,25 +20952,44 @@
       <c r="M13" s="44">
         <v>7</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="27">
+        <v>46175</v>
+      </c>
       <c r="O13" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Shakoor</v>
       </c>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
+      <c r="Q13" s="12">
+        <v>160</v>
+      </c>
+      <c r="R13" s="12">
+        <v>120</v>
+      </c>
       <c r="S13" s="12"/>
       <c r="T13" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="U13" s="12">
+        <v>440</v>
+      </c>
+      <c r="V13" s="12">
+        <v>440</v>
+      </c>
+      <c r="W13" s="12">
+        <v>520</v>
+      </c>
       <c r="X13" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="6"/>
+        <v>42</v>
+      </c>
+      <c r="Z13" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
@@ -20929,15 +21039,15 @@
       <c r="O14" s="10"/>
       <c r="P14" s="14">
         <f t="shared" ref="P14:X14" si="9">SUM(P8:P13)</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="R14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="9"/>
@@ -20945,27 +21055,27 @@
       </c>
       <c r="T14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="V14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="W14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="X14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>121.65</v>
       </c>
       <c r="Y14" s="35">
         <f>P14+Q14+R14+S14+U14+V14+W14</f>
-        <v>0</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.35">
@@ -21007,11 +21117,11 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="13">
         <f>Q14/20</f>
-        <v>0</v>
+        <v>18.05</v>
       </c>
       <c r="R15" s="13">
         <f t="shared" ref="R15:S15" si="11">R14/20</f>
-        <v>0</v>
+        <v>18.45</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="11"/>
@@ -21020,15 +21130,15 @@
       <c r="T15" s="13"/>
       <c r="U15" s="13">
         <f t="shared" ref="U15:W15" si="12">U14/20</f>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="V15" s="13">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="W15" s="13">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>46.35</v>
       </c>
       <c r="X15" s="13"/>
     </row>
@@ -21073,15 +21183,15 @@
       </c>
       <c r="P16" s="36">
         <f>P15+P14</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="Q16" s="36">
         <f t="shared" ref="Q16:S16" si="14">Q15+Q14</f>
-        <v>0</v>
+        <v>379.05</v>
       </c>
       <c r="R16" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>387.45</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="14"/>
@@ -21090,15 +21200,15 @@
       <c r="T16" s="36"/>
       <c r="U16" s="36">
         <f t="shared" ref="U16:W16" si="15">U15+U14</f>
-        <v>0</v>
+        <v>787.5</v>
       </c>
       <c r="V16" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>793.8</v>
       </c>
       <c r="W16" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>973.35</v>
       </c>
       <c r="X16" s="36"/>
     </row>
@@ -21147,15 +21257,15 @@
       </c>
       <c r="P17" s="36">
         <f>P14/40</f>
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q17" s="36">
         <f t="shared" ref="Q17:S17" si="17">Q14/40</f>
-        <v>0</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="R17" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9.2249999999999996</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="17"/>
@@ -21164,20 +21274,20 @@
       <c r="T17" s="36"/>
       <c r="U17" s="36">
         <f t="shared" ref="U17:W17" si="18">U14/40</f>
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="V17" s="36">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="W17" s="36">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>23.175000000000001</v>
       </c>
       <c r="X17" s="36"/>
       <c r="Y17" s="35">
         <f>SUM(P17:W17)</f>
-        <v>0</v>
+        <v>93.575000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
@@ -24089,24 +24199,41 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="12">
+        <v>72</v>
+      </c>
+      <c r="D8" s="12">
+        <v>72</v>
+      </c>
+      <c r="E8" s="12">
+        <v>48</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="H8" s="12">
+        <v>40</v>
+      </c>
+      <c r="I8" s="12">
+        <v>20</v>
+      </c>
+      <c r="J8" s="12">
+        <v>60</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
+        <v>7.8</v>
+      </c>
+      <c r="M8" s="44">
+        <v>7</v>
       </c>
       <c r="N8" s="27">
         <v>46176</v>
@@ -24142,24 +24269,41 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="12">
+        <v>34</v>
+      </c>
+      <c r="D9" s="12">
+        <v>32</v>
+      </c>
+      <c r="E9" s="12">
+        <v>26</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
       <c r="G9" s="28">
         <f t="shared" ref="G9:G13" si="0">SUM(D9:F9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+        <v>2.9</v>
+      </c>
+      <c r="H9" s="12">
+        <v>42</v>
+      </c>
+      <c r="I9" s="12">
+        <v>36</v>
+      </c>
+      <c r="J9" s="12">
+        <v>52</v>
+      </c>
       <c r="K9" s="28">
         <f t="shared" ref="K9:K13" si="1">SUM(H9:J9)/20</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
+        <v>5.55</v>
+      </c>
+      <c r="M9" s="44">
+        <v>7</v>
       </c>
       <c r="N9" s="27">
         <v>46176</v>
@@ -24195,24 +24339,41 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="C10" s="12">
+        <v>100</v>
+      </c>
+      <c r="D10" s="12">
+        <v>100</v>
+      </c>
+      <c r="E10" s="12">
+        <v>30</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
       <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="H10" s="12">
+        <v>45</v>
+      </c>
+      <c r="I10" s="12">
+        <v>60</v>
+      </c>
+      <c r="J10" s="12">
+        <v>155</v>
+      </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.25</v>
+      </c>
+      <c r="M10" s="44">
+        <v>9</v>
       </c>
       <c r="N10" s="27">
         <v>46176</v>
@@ -24248,24 +24409,41 @@
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="C11" s="12">
+        <v>612</v>
+      </c>
+      <c r="D11" s="12">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12">
+        <v>20</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
       <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="H11" s="12">
+        <v>145</v>
+      </c>
+      <c r="I11" s="12">
+        <v>145</v>
+      </c>
+      <c r="J11" s="12">
+        <v>110</v>
+      </c>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26.3</v>
+      </c>
+      <c r="M11" s="41">
+        <v>7</v>
       </c>
       <c r="N11" s="27">
         <v>46176</v>
@@ -24301,24 +24479,41 @@
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="C12" s="12">
+        <v>72</v>
+      </c>
+      <c r="D12" s="12">
+        <v>72</v>
+      </c>
+      <c r="E12" s="12">
+        <v>66</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
       <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
+        <v>6.9</v>
+      </c>
+      <c r="H12" s="12">
+        <v>112</v>
+      </c>
+      <c r="I12" s="12">
+        <v>100</v>
+      </c>
+      <c r="J12" s="12">
+        <v>112</v>
+      </c>
       <c r="K12" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="L12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13.35</v>
+      </c>
+      <c r="M12" s="41">
+        <v>4</v>
       </c>
       <c r="N12" s="27">
         <v>46176</v>
@@ -24388,15 +24583,15 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="7">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="7"/>
@@ -24404,27 +24599,27 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24.299999999999997</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>61.7</v>
       </c>
       <c r="L14" s="35">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="10"/>
@@ -24477,11 +24672,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="9">E14/20</f>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="9"/>
@@ -24490,15 +24685,15 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>18.05</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>24.45</v>
       </c>
       <c r="K15" s="13"/>
       <c r="N15" s="13"/>
@@ -24540,15 +24735,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:J16" si="12">D15+D14</f>
-        <v>0</v>
+        <v>310.8</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>199.5</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="12"/>
@@ -24557,15 +24752,15 @@
       <c r="G16" s="36"/>
       <c r="H16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>403.2</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>379.05</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>513.45000000000005</v>
       </c>
       <c r="K16" s="36"/>
       <c r="N16" s="13"/>
@@ -24610,15 +24805,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:J17" si="15">D14/40</f>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="15"/>
@@ -24627,20 +24822,20 @@
       <c r="G17" s="36"/>
       <c r="H17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>9.0250000000000004</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>12.225</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="35">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>65.25</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="39" t="s">

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3BD427-A6A9-4D22-AA22-47D7F7D32963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF520682-0F73-4459-B445-47723F01490C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="2" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="3" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="41">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -630,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -792,6 +792,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -24312,24 +24318,41 @@
         <f t="shared" ref="O9:O12" si="3">B9</f>
         <v>Salman</v>
       </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="P9" s="12">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>26</v>
+      </c>
+      <c r="R9" s="12">
+        <v>26</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
       <c r="T9" s="28">
         <f t="shared" ref="T9:T13" si="4">SUM(Q9:S9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
+        <v>2.6</v>
+      </c>
+      <c r="U9" s="12">
+        <v>29</v>
+      </c>
+      <c r="V9" s="12">
+        <v>36</v>
+      </c>
+      <c r="W9" s="12">
+        <v>52</v>
+      </c>
       <c r="X9" s="28">
         <f t="shared" ref="X9:X13" si="5">SUM(U9:W9)/20</f>
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="Y9:Y13" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
+        <v>5.0750000000000002</v>
+      </c>
+      <c r="Z9" s="68">
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
@@ -24382,24 +24405,41 @@
         <f t="shared" si="3"/>
         <v>Zesahn</v>
       </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="P10" s="12">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>100</v>
+      </c>
+      <c r="R10" s="12">
+        <v>30</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
+        <v>6.5</v>
+      </c>
+      <c r="U10" s="12">
+        <v>45</v>
+      </c>
+      <c r="V10" s="12">
+        <v>60</v>
+      </c>
+      <c r="W10" s="12">
+        <v>155</v>
+      </c>
       <c r="X10" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y10">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12.25</v>
+      </c>
+      <c r="Z10" s="68">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
@@ -24522,24 +24562,39 @@
         <f t="shared" si="3"/>
         <v>Mubeen</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
+      <c r="P12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0</v>
+      </c>
       <c r="S12" s="12"/>
       <c r="T12" s="28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
+      <c r="U12" s="12">
+        <v>40</v>
+      </c>
+      <c r="V12" s="12">
+        <v>40</v>
+      </c>
+      <c r="W12" s="12">
+        <v>40</v>
+      </c>
       <c r="X12" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Z12" s="68">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
@@ -24560,22 +24615,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
+      <c r="N13" s="27">
+        <v>46176</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
+      <c r="Q13" s="12">
+        <v>198</v>
+      </c>
+      <c r="R13" s="12">
+        <v>237</v>
+      </c>
       <c r="S13" s="12"/>
       <c r="T13" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
+        <v>21.75</v>
+      </c>
+      <c r="U13" s="12">
+        <v>359</v>
+      </c>
+      <c r="V13" s="12">
+        <v>78</v>
+      </c>
+      <c r="W13" s="12">
+        <v>358</v>
+      </c>
       <c r="X13" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>39.75</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="6"/>
+        <v>30.75</v>
+      </c>
+      <c r="Z13" s="68">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
@@ -24625,15 +24701,15 @@
       <c r="O14" s="10"/>
       <c r="P14" s="14">
         <f t="shared" ref="P14:X14" si="8">SUM(P8:P13)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="R14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="8"/>
@@ -24641,27 +24717,27 @@
       </c>
       <c r="T14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30.85</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="V14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="W14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="X14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="Y14" s="35">
         <f>P14+Q14+R14+S14+U14+V14+W14</f>
-        <v>0</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.35">
@@ -24703,11 +24779,11 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="13">
         <f>Q14/20</f>
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="R15" s="13">
         <f t="shared" ref="R15:S15" si="10">R14/20</f>
-        <v>0</v>
+        <v>14.65</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="10"/>
@@ -24716,15 +24792,15 @@
       <c r="T15" s="13"/>
       <c r="U15" s="13">
         <f t="shared" ref="U15:W15" si="11">U14/20</f>
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="V15" s="13">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="W15" s="13">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>30.25</v>
       </c>
       <c r="X15" s="13"/>
     </row>
@@ -24769,15 +24845,15 @@
       </c>
       <c r="P16" s="36">
         <f>P15+P14</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="Q16" s="36">
         <f t="shared" ref="Q16:S16" si="13">Q15+Q14</f>
-        <v>0</v>
+        <v>340.2</v>
       </c>
       <c r="R16" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>307.64999999999998</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="13"/>
@@ -24786,15 +24862,15 @@
       <c r="T16" s="36"/>
       <c r="U16" s="36">
         <f t="shared" ref="U16:W16" si="14">U15+U14</f>
-        <v>0</v>
+        <v>496.65</v>
       </c>
       <c r="V16" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>224.7</v>
       </c>
       <c r="W16" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>635.25</v>
       </c>
       <c r="X16" s="36"/>
     </row>
@@ -24843,15 +24919,15 @@
       </c>
       <c r="P17" s="36">
         <f>P14/40</f>
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" s="36">
         <f t="shared" ref="Q17:S17" si="16">Q14/40</f>
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="R17" s="36">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>7.3250000000000002</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="16"/>
@@ -24860,20 +24936,20 @@
       <c r="T17" s="36"/>
       <c r="U17" s="36">
         <f t="shared" ref="U17:W17" si="17">U14/40</f>
-        <v>0</v>
+        <v>11.824999999999999</v>
       </c>
       <c r="V17" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W17" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>15.125</v>
       </c>
       <c r="X17" s="36"/>
       <c r="Y17" s="35">
         <f>SUM(P17:W17)</f>
-        <v>0</v>
+        <v>51.074999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
@@ -25173,24 +25249,41 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="12">
+        <v>22</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
         <v>0</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="H8" s="12">
+        <v>43</v>
+      </c>
+      <c r="I8" s="12">
+        <v>57</v>
+      </c>
+      <c r="J8" s="12">
+        <v>39</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="M8" s="68">
+        <v>6</v>
       </c>
       <c r="N8" s="27">
         <v>46177</v>
@@ -25226,30 +25319,47 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="12">
+        <v>120</v>
+      </c>
+      <c r="D9" s="12">
+        <v>80</v>
+      </c>
+      <c r="E9" s="12">
+        <v>90</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
       <c r="G9" s="28">
         <f t="shared" ref="G9:G13" si="0">SUM(D9:F9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+        <v>8.5</v>
+      </c>
+      <c r="H9" s="12">
+        <v>50</v>
+      </c>
+      <c r="I9" s="12">
+        <v>40</v>
+      </c>
+      <c r="J9" s="12">
+        <v>50</v>
+      </c>
       <c r="K9" s="28">
         <f t="shared" ref="K9:K13" si="1">SUM(H9:J9)/20</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="L9:L13" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>10.75</v>
+      </c>
+      <c r="M9" s="68">
+        <v>3</v>
       </c>
       <c r="N9" s="27">
         <v>46177</v>
       </c>
       <c r="O9" s="10" t="str">
-        <f t="shared" ref="O9:O12" si="3">B9</f>
+        <f t="shared" ref="O9:O13" si="3">B9</f>
         <v>Salman</v>
       </c>
       <c r="P9" s="12"/>
@@ -25279,24 +25389,41 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="C10" s="12">
+        <v>262</v>
+      </c>
+      <c r="D10" s="12">
+        <v>70</v>
+      </c>
+      <c r="E10" s="12">
+        <v>30</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
       <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="H10" s="12">
+        <v>117</v>
+      </c>
+      <c r="I10" s="12">
+        <v>60</v>
+      </c>
+      <c r="J10" s="12">
+        <v>165</v>
+      </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="M10" s="68">
+        <v>12</v>
       </c>
       <c r="N10" s="27">
         <v>46177</v>
@@ -25332,24 +25459,41 @@
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="C11" s="12">
+        <v>182</v>
+      </c>
+      <c r="D11" s="12">
+        <v>95</v>
+      </c>
+      <c r="E11" s="12">
+        <v>75</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
       <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
+        <v>8.5</v>
+      </c>
+      <c r="H11" s="12">
+        <v>218</v>
+      </c>
+      <c r="I11" s="12">
+        <v>148</v>
+      </c>
+      <c r="J11" s="12">
+        <v>138</v>
+      </c>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="L11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21.4</v>
+      </c>
+      <c r="M11" s="69">
+        <v>10</v>
       </c>
       <c r="N11" s="27">
         <v>46177</v>
@@ -25383,24 +25527,41 @@
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="C12" s="12">
+        <v>104</v>
+      </c>
+      <c r="D12" s="12">
+        <v>74</v>
+      </c>
+      <c r="E12" s="12">
+        <v>62</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
       <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
+        <v>6.8</v>
+      </c>
+      <c r="H12" s="12">
+        <v>82</v>
+      </c>
+      <c r="I12" s="12">
+        <v>128</v>
+      </c>
+      <c r="J12" s="12">
+        <v>152</v>
+      </c>
       <c r="K12" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="L12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15.05</v>
+      </c>
+      <c r="M12" s="68">
+        <v>9</v>
       </c>
       <c r="N12" s="11"/>
       <c r="O12" s="10" t="str">
@@ -25429,24 +25590,46 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="D13" s="12">
+        <v>200</v>
+      </c>
+      <c r="E13" s="12">
+        <v>200</v>
+      </c>
       <c r="F13" s="12"/>
       <c r="G13" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="H13" s="12">
+        <v>400</v>
+      </c>
+      <c r="I13" s="12">
+        <v>400</v>
+      </c>
+      <c r="J13" s="12">
+        <v>400</v>
+      </c>
       <c r="K13" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="M13" s="68">
+        <v>3</v>
       </c>
       <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
+      <c r="O13" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Shakoor </v>
+      </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
@@ -25468,15 +25651,15 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="7">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="7"/>
@@ -25484,27 +25667,27 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>48.8</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>944</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>134.35</v>
       </c>
       <c r="L14" s="35">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
+        <v>4353</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="10"/>
@@ -25557,11 +25740,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>25.95</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="9">E14/20</f>
-        <v>0</v>
+        <v>22.85</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="9"/>
@@ -25570,15 +25753,15 @@
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>41.65</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="K15" s="13"/>
       <c r="N15" s="13"/>
@@ -25620,15 +25803,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:J16" si="12">D15+D14</f>
-        <v>0</v>
+        <v>544.95000000000005</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>479.85</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="12"/>
@@ -25637,15 +25820,15 @@
       <c r="G16" s="36"/>
       <c r="H16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>955.5</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>874.65</v>
       </c>
       <c r="J16" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>991.2</v>
       </c>
       <c r="K16" s="36"/>
       <c r="N16" s="13"/>
@@ -25690,15 +25873,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:J17" si="15">D14/40</f>
-        <v>0</v>
+        <v>12.975</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>11.425000000000001</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="15"/>
@@ -25707,20 +25890,20 @@
       <c r="G17" s="36"/>
       <c r="H17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>20.824999999999999</v>
       </c>
       <c r="J17" s="36">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="35">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>108.82500000000002</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="39" t="s">

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF520682-0F73-4459-B445-47723F01490C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92923D8C-0AB8-4798-93D5-404E51964FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="3" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="4" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -630,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -792,12 +792,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -24351,7 +24345,7 @@
         <f t="shared" ref="Y9:Y13" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
         <v>5.0750000000000002</v>
       </c>
-      <c r="Z9" s="68">
+      <c r="Z9" s="44">
         <v>7</v>
       </c>
     </row>
@@ -24438,7 +24432,7 @@
         <f t="shared" si="6"/>
         <v>12.25</v>
       </c>
-      <c r="Z10" s="68">
+      <c r="Z10" s="44">
         <v>9</v>
       </c>
     </row>
@@ -24593,7 +24587,7 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="Z12" s="68">
+      <c r="Z12" s="44">
         <v>1</v>
       </c>
     </row>
@@ -24650,7 +24644,7 @@
         <f t="shared" si="6"/>
         <v>30.75</v>
       </c>
-      <c r="Z13" s="68">
+      <c r="Z13" s="44">
         <v>3</v>
       </c>
     </row>
@@ -25282,7 +25276,7 @@
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>4.0250000000000004</v>
       </c>
-      <c r="M8" s="68">
+      <c r="M8" s="44">
         <v>6</v>
       </c>
       <c r="N8" s="27">
@@ -25292,24 +25286,41 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="P8" s="12">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>36</v>
+      </c>
+      <c r="R8" s="12">
+        <v>32</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
       <c r="T8" s="28">
         <f>SUM(Q8:S8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
+        <v>3.4</v>
+      </c>
+      <c r="U8" s="12">
+        <v>20</v>
+      </c>
+      <c r="V8" s="12">
+        <v>20</v>
+      </c>
+      <c r="W8" s="12">
+        <v>40</v>
+      </c>
       <c r="X8" s="28">
         <f>SUM(U8:W8)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y8">
         <f>SUM(P8:S8,U8,V8,W8)/40</f>
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="Z8" s="44">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.35">
@@ -25352,7 +25363,7 @@
         <f t="shared" ref="L9:L13" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
         <v>10.75</v>
       </c>
-      <c r="M9" s="68">
+      <c r="M9" s="44">
         <v>3</v>
       </c>
       <c r="N9" s="27">
@@ -25422,7 +25433,7 @@
         <f t="shared" si="2"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="44">
         <v>12</v>
       </c>
       <c r="N10" s="27">
@@ -25432,24 +25443,41 @@
         <f t="shared" si="3"/>
         <v>Zesahn</v>
       </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="P10" s="12">
+        <v>170</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>30</v>
+      </c>
+      <c r="R10" s="12">
+        <v>30</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="U10" s="12">
+        <v>77</v>
+      </c>
+      <c r="V10" s="12">
+        <v>60</v>
+      </c>
+      <c r="W10" s="12">
+        <v>85</v>
+      </c>
       <c r="X10" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="Y10">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11.3</v>
+      </c>
+      <c r="Z10" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
@@ -25492,7 +25520,7 @@
         <f t="shared" si="2"/>
         <v>21.4</v>
       </c>
-      <c r="M11" s="69">
+      <c r="M11" s="41">
         <v>10</v>
       </c>
       <c r="N11" s="27">
@@ -25502,24 +25530,46 @@
         <f t="shared" si="3"/>
         <v>Umair</v>
       </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
+      <c r="P11" s="12">
+        <f>182+572</f>
+        <v>754</v>
+      </c>
+      <c r="Q11" s="12">
+        <f>95+20</f>
+        <v>115</v>
+      </c>
+      <c r="R11" s="12">
+        <f>75+20</f>
+        <v>95</v>
+      </c>
       <c r="S11" s="12"/>
       <c r="T11" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
+        <v>10.5</v>
+      </c>
+      <c r="U11" s="12">
+        <f>218+145</f>
+        <v>363</v>
+      </c>
+      <c r="V11" s="12">
+        <f>138+145</f>
+        <v>283</v>
+      </c>
+      <c r="W11" s="12">
+        <f>138+110</f>
+        <v>248</v>
+      </c>
       <c r="X11" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="Y11">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>46.45</v>
+      </c>
+      <c r="Z11" s="44">
+        <f>8+6</f>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
@@ -25560,7 +25610,7 @@
         <f t="shared" si="2"/>
         <v>15.05</v>
       </c>
-      <c r="M12" s="68">
+      <c r="M12" s="44">
         <v>9</v>
       </c>
       <c r="N12" s="11"/>
@@ -25568,24 +25618,41 @@
         <f t="shared" si="3"/>
         <v>Mubeen</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
+      <c r="P12" s="12">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>74</v>
+      </c>
+      <c r="R12" s="12">
+        <v>62</v>
+      </c>
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
       <c r="T12" s="28">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
+        <v>6.8</v>
+      </c>
+      <c r="U12" s="12">
+        <v>82</v>
+      </c>
+      <c r="V12" s="12">
+        <v>128</v>
+      </c>
+      <c r="W12" s="12">
+        <v>152</v>
+      </c>
       <c r="X12" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="Y12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15.05</v>
+      </c>
+      <c r="Z12" s="44">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
@@ -25622,7 +25689,7 @@
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="M13" s="68">
+      <c r="M13" s="44">
         <v>3</v>
       </c>
       <c r="N13" s="11"/>
@@ -25693,15 +25760,15 @@
       <c r="O14" s="10"/>
       <c r="P14" s="14">
         <f t="shared" ref="P14:X14" si="8">SUM(P8:P13)</f>
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="R14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="8"/>
@@ -25709,27 +25776,27 @@
       </c>
       <c r="T14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="V14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="W14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="X14" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="Y14" s="35">
         <f>P14+Q14+R14+S14+U14+V14+W14</f>
-        <v>0</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.35">
@@ -25771,11 +25838,11 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="13">
         <f>Q14/20</f>
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="R15" s="13">
         <f t="shared" ref="R15:S15" si="10">R14/20</f>
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="10"/>
@@ -25784,15 +25851,15 @@
       <c r="T15" s="13"/>
       <c r="U15" s="13">
         <f t="shared" ref="U15:W15" si="11">U14/20</f>
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="V15" s="13">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="W15" s="13">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>26.25</v>
       </c>
       <c r="X15" s="13"/>
     </row>
@@ -25837,15 +25904,15 @@
       </c>
       <c r="P16" s="36">
         <f>P15+P14</f>
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="Q16" s="36">
         <f t="shared" ref="Q16:S16" si="13">Q15+Q14</f>
-        <v>0</v>
+        <v>267.75</v>
       </c>
       <c r="R16" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>229.95</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="13"/>
@@ -25854,15 +25921,15 @@
       <c r="T16" s="36"/>
       <c r="U16" s="36">
         <f t="shared" ref="U16:W16" si="14">U15+U14</f>
-        <v>0</v>
+        <v>569.1</v>
       </c>
       <c r="V16" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>515.54999999999995</v>
       </c>
       <c r="W16" s="36">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>551.25</v>
       </c>
       <c r="X16" s="36"/>
     </row>
@@ -25911,15 +25978,15 @@
       </c>
       <c r="P17" s="36">
         <f>P14/40</f>
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="Q17" s="36">
         <f t="shared" ref="Q17:S17" si="16">Q14/40</f>
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="R17" s="36">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>5.4749999999999996</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="16"/>
@@ -25928,20 +25995,20 @@
       <c r="T17" s="36"/>
       <c r="U17" s="36">
         <f t="shared" ref="U17:W17" si="17">U14/40</f>
-        <v>0</v>
+        <v>13.55</v>
       </c>
       <c r="V17" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>12.275</v>
       </c>
       <c r="W17" s="36">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>13.125</v>
       </c>
       <c r="X17" s="36"/>
       <c r="Y17" s="35">
         <f>SUM(P17:W17)</f>
-        <v>0</v>
+        <v>78.000000000000014</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
@@ -26248,13 +26315,15 @@
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="28">
-        <v>20</v>
+        <f>SUM(C8:F8)/20</f>
+        <v>0</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="28">
-        <v>7</v>
+        <f>SUM(G8:J8)/20</f>
+        <v>0</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
@@ -26272,13 +26341,15 @@
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="28">
-        <v>20</v>
+        <f>SUM(P8:S8)/20</f>
+        <v>0</v>
       </c>
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="28">
-        <v>7</v>
+        <f t="shared" ref="X8:X13" si="0">SUM(T8:W8)/20</f>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f>SUM(P8:S8,U8,V8,W8)/40</f>
@@ -26292,28 +26363,47 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="12">
+        <v>110</v>
+      </c>
+      <c r="D9" s="12">
+        <v>82</v>
+      </c>
+      <c r="E9" s="12">
+        <v>26</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
       <c r="G9" s="28">
-        <v>20</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+        <f t="shared" ref="G9:G13" si="1">SUM(C9:F9)/20</f>
+        <v>10.9</v>
+      </c>
+      <c r="H9" s="12">
+        <v>60</v>
+      </c>
+      <c r="I9" s="12">
+        <v>25</v>
+      </c>
+      <c r="J9" s="12">
+        <v>65</v>
+      </c>
       <c r="K9" s="28">
-        <v>7</v>
+        <f t="shared" ref="K9:K13" si="2">SUM(G9:J9)/20</f>
+        <v>8.0449999999999999</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="L9:L12" si="3">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="M9" s="44">
+        <v>8</v>
       </c>
       <c r="N9" s="27">
         <v>46178</v>
       </c>
       <c r="O9" s="10" t="str">
-        <f t="shared" ref="O9:O12" si="1">B9</f>
+        <f t="shared" ref="O9:O12" si="4">B9</f>
         <v>Salman</v>
       </c>
       <c r="P9" s="12"/>
@@ -26321,16 +26411,18 @@
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="28">
-        <v>20</v>
+        <f t="shared" ref="T9:T13" si="5">SUM(P9:S9)/20</f>
+        <v>0</v>
       </c>
       <c r="U9" s="12"/>
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
       <c r="X9" s="28">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="2">SUM(P9:S9,U9,V9,W9)/40</f>
+        <f t="shared" ref="Y9:Y12" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -26341,28 +26433,47 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="C10" s="12">
+        <v>200</v>
+      </c>
+      <c r="D10" s="12">
+        <v>40</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
       <c r="G10" s="28">
-        <v>20</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="H10" s="12">
+        <v>130</v>
+      </c>
+      <c r="I10" s="12">
+        <v>50</v>
+      </c>
+      <c r="J10" s="12">
+        <v>260</v>
+      </c>
       <c r="K10" s="28">
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>22.6</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="M10" s="44">
+        <v>10</v>
       </c>
       <c r="N10" s="27">
         <v>46178</v>
       </c>
       <c r="O10" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Zesahn</v>
       </c>
       <c r="P10" s="12"/>
@@ -26370,16 +26481,18 @@
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="28">
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U10" s="12"/>
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
       <c r="X10" s="28">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -26388,26 +26501,43 @@
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="C11" s="12">
+        <v>280</v>
+      </c>
+      <c r="D11" s="12">
+        <v>180</v>
+      </c>
+      <c r="E11" s="12">
+        <v>140</v>
+      </c>
       <c r="F11" s="12"/>
       <c r="G11" s="28">
-        <v>20</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="12">
+        <v>135</v>
+      </c>
+      <c r="I11" s="12">
+        <v>135</v>
+      </c>
+      <c r="J11" s="12">
+        <v>170</v>
+      </c>
       <c r="K11" s="28">
+        <f t="shared" si="2"/>
+        <v>23.5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="M11" s="44">
         <v>7</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="N11" s="11"/>
       <c r="O11" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Umair</v>
       </c>
       <c r="P11" s="12"/>
@@ -26415,16 +26545,18 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="28">
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
       <c r="X11" s="28">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -26433,26 +26565,45 @@
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="C12" s="12">
+        <v>12</v>
+      </c>
+      <c r="D12" s="12">
+        <v>32</v>
+      </c>
+      <c r="E12" s="12">
+        <v>32</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
       <c r="G12" s="28">
-        <v>20</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+      <c r="H12" s="12">
+        <v>110</v>
+      </c>
+      <c r="I12" s="12">
+        <v>85</v>
+      </c>
+      <c r="J12" s="12">
+        <v>85</v>
+      </c>
       <c r="K12" s="28">
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>14.190000000000001</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>8.9</v>
+      </c>
+      <c r="M12" s="44">
+        <v>5</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Mubeen</v>
       </c>
       <c r="P12" s="12"/>
@@ -26460,16 +26611,18 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="28">
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="28">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -26481,13 +26634,15 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="28">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="28">
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="11"/>
@@ -26496,13 +26651,15 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="28">
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="28">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
@@ -26543,32 +26700,32 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <f t="shared" ref="C15" si="3">SUM(C8:C14)</f>
-        <v>0</v>
+        <f t="shared" ref="C15" si="7">SUM(C8:C14)</f>
+        <v>602</v>
       </c>
       <c r="D15" s="14">
         <f>D14/20</f>
         <v>0</v>
       </c>
       <c r="E15" s="14">
-        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <f t="shared" ref="E15:J15" si="8">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K15" s="14"/>
@@ -26577,7 +26734,7 @@
         <v>22</v>
       </c>
       <c r="P15" s="14">
-        <f t="shared" ref="P15" si="5">SUM(P8:P14)</f>
+        <f t="shared" ref="P15" si="9">SUM(P8:P14)</f>
         <v>0</v>
       </c>
       <c r="Q15" s="14">
@@ -26585,24 +26742,24 @@
         <v>0</v>
       </c>
       <c r="R15" s="14">
-        <f t="shared" ref="R15:S15" si="6">R14/20</f>
+        <f t="shared" ref="R15:S15" si="10">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T15" s="14"/>
       <c r="U15" s="14">
-        <f t="shared" ref="U15:W15" si="7">U14/20</f>
+        <f t="shared" ref="U15:W15" si="11">U14/20</f>
         <v>0</v>
       </c>
       <c r="V15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="W15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="X15" s="14"/>
@@ -26614,31 +26771,31 @@
       </c>
       <c r="C16" s="13">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" ref="D16:J16" si="8">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="12">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K16" s="13"/>
@@ -26651,28 +26808,28 @@
         <v>0</v>
       </c>
       <c r="Q16" s="13">
-        <f t="shared" ref="Q16:S16" si="9">Q15+Q14</f>
+        <f t="shared" ref="Q16:S16" si="13">Q15+Q14</f>
         <v>0</v>
       </c>
       <c r="R16" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T16" s="13"/>
       <c r="U16" s="13">
-        <f t="shared" ref="U16:W16" si="10">U15+U14</f>
+        <f t="shared" ref="U16:W16" si="14">U15+U14</f>
         <v>0</v>
       </c>
       <c r="V16" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="W16" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="X16" s="13"/>
@@ -26718,35 +26875,35 @@
       <c r="B18" s="1"/>
       <c r="C18" s="41"/>
       <c r="D18" s="26">
-        <f t="shared" ref="D18:K18" si="11">D15/40</f>
+        <f t="shared" ref="D18:K18" si="15">D15/40</f>
         <v>0</v>
       </c>
       <c r="E18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K18" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92923D8C-0AB8-4798-93D5-404E51964FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02F07B9-7717-45F5-A026-E85F060E1D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="4" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="7" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="41">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -630,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -757,6 +757,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -792,6 +796,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1138,57 +1145,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="B2" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1196,18 +1203,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1559,103 +1566,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1663,35 +1670,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2433,103 +2440,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2537,35 +2544,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3303,103 +3310,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3407,35 +3414,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4176,103 +4183,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4280,35 +4287,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5049,103 +5056,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5153,35 +5160,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5935,103 +5942,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6039,35 +6046,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6805,103 +6812,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6909,35 +6916,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7674,103 +7681,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7778,35 +7785,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8552,103 +8559,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8656,35 +8663,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9436,103 +9443,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9540,35 +9547,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10330,58 +10337,58 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
       <c r="AB2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
       <c r="AB3">
         <v>14</v>
       </c>
@@ -10394,51 +10401,51 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10446,35 +10453,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11369,103 +11376,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11473,35 +11480,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12248,103 +12255,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12352,35 +12359,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13144,103 +13151,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13248,35 +13255,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14014,103 +14021,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14118,35 +14125,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14910,103 +14917,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15014,35 +15021,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15806,103 +15813,103 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15910,35 +15917,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -16729,103 +16736,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16833,35 +16840,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -17599,103 +17606,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -17703,35 +17710,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18473,103 +18480,103 @@
     </row>
     <row r="2" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -18577,35 +18584,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -19395,103 +19402,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -19499,35 +19506,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -20280,103 +20287,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -20384,35 +20391,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -21367,103 +21374,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -21471,35 +21478,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -22237,103 +22244,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -22341,35 +22348,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -23108,103 +23115,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -23212,35 +23219,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -23978,103 +23985,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -24082,35 +24089,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -25022,103 +25029,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -25126,35 +25133,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -26089,103 +26096,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -26193,35 +26200,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -26307,47 +26314,35 @@
       <c r="A8" s="27">
         <v>46178</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="28">
-        <f>SUM(C8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="28">
-        <f>SUM(G8:J8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
       <c r="N8" s="27">
         <v>46178</v>
       </c>
-      <c r="O8" s="10" t="str">
+      <c r="O8" s="43">
         <f>B8</f>
-        <v>Furqan</v>
-      </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="28">
+        <v>0</v>
+      </c>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29">
         <f>SUM(P8:S8)/20</f>
         <v>0</v>
       </c>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="28">
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29">
         <f t="shared" ref="X8:X13" si="0">SUM(T8:W8)/20</f>
         <v>0</v>
       </c>
@@ -26360,69 +26355,41 @@
       <c r="A9" s="27">
         <v>46178</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="12">
-        <v>110</v>
-      </c>
-      <c r="D9" s="12">
-        <v>82</v>
-      </c>
-      <c r="E9" s="12">
-        <v>26</v>
-      </c>
-      <c r="F9" s="12">
-        <v>0</v>
-      </c>
-      <c r="G9" s="28">
-        <f t="shared" ref="G9:G13" si="1">SUM(C9:F9)/20</f>
-        <v>10.9</v>
-      </c>
-      <c r="H9" s="12">
-        <v>60</v>
-      </c>
-      <c r="I9" s="12">
-        <v>25</v>
-      </c>
-      <c r="J9" s="12">
-        <v>65</v>
-      </c>
-      <c r="K9" s="28">
-        <f t="shared" ref="K9:K13" si="2">SUM(G9:J9)/20</f>
-        <v>8.0449999999999999</v>
-      </c>
-      <c r="L9">
-        <f t="shared" ref="L9:L12" si="3">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="M9" s="44">
-        <v>8</v>
-      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="M9" s="44"/>
       <c r="N9" s="27">
         <v>46178</v>
       </c>
-      <c r="O9" s="10" t="str">
-        <f t="shared" ref="O9:O12" si="4">B9</f>
-        <v>Salman</v>
-      </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="28">
-        <f t="shared" ref="T9:T13" si="5">SUM(P9:S9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="28">
+      <c r="O9" s="43">
+        <f t="shared" ref="O9:O12" si="1">B9</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29">
+        <f t="shared" ref="T9:T13" si="2">SUM(P9:S9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="6">SUM(P9:S9,U9,V9,W9)/40</f>
+        <f t="shared" ref="Y9:Y12" si="3">SUM(P9:S9,U9,V9,W9)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -26430,265 +26397,183 @@
       <c r="A10" s="27">
         <v>46178</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="12">
-        <v>200</v>
-      </c>
-      <c r="D10" s="12">
-        <v>40</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="H10" s="12">
-        <v>130</v>
-      </c>
-      <c r="I10" s="12">
-        <v>50</v>
-      </c>
-      <c r="J10" s="12">
-        <v>260</v>
-      </c>
-      <c r="K10" s="28">
-        <f t="shared" si="2"/>
-        <v>22.6</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-      <c r="M10" s="44">
-        <v>10</v>
-      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="M10" s="44"/>
       <c r="N10" s="27">
         <v>46178</v>
       </c>
-      <c r="O10" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Zesahn</v>
-      </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="28">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="28">
+      <c r="O10" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="12">
-        <v>280</v>
-      </c>
-      <c r="D11" s="12">
-        <v>180</v>
-      </c>
-      <c r="E11" s="12">
-        <v>140</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="28">
+      <c r="B11" s="55"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="43">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="H11" s="12">
-        <v>135</v>
-      </c>
-      <c r="I11" s="12">
-        <v>135</v>
-      </c>
-      <c r="J11" s="12">
-        <v>170</v>
-      </c>
-      <c r="K11" s="28">
+        <v>0</v>
+      </c>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29">
         <f t="shared" si="2"/>
-        <v>23.5</v>
-      </c>
-      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
         <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="M11" s="44">
-        <v>7</v>
-      </c>
-      <c r="N11" s="11"/>
-      <c r="O11" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Umair</v>
-      </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="28">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>
-      <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="12">
-        <v>12</v>
-      </c>
-      <c r="D12" s="12">
-        <v>32</v>
-      </c>
-      <c r="E12" s="12">
-        <v>32</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="28">
+      <c r="B12" s="55"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="43">
         <f t="shared" si="1"/>
-        <v>3.8</v>
-      </c>
-      <c r="H12" s="12">
-        <v>110</v>
-      </c>
-      <c r="I12" s="12">
-        <v>85</v>
-      </c>
-      <c r="J12" s="12">
-        <v>85</v>
-      </c>
-      <c r="K12" s="28">
+        <v>0</v>
+      </c>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29">
         <f t="shared" si="2"/>
-        <v>14.190000000000001</v>
-      </c>
-      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y12">
         <f t="shared" si="3"/>
-        <v>8.9</v>
-      </c>
-      <c r="M12" s="44">
-        <v>5</v>
-      </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>Mubeen</v>
-      </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="28">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="28">
+      <c r="B13" s="55"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29">
+        <f t="shared" ref="G13" si="4">SUM(C13:F13)/20</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29">
+        <f t="shared" ref="K13" si="5">SUM(G13:J13)/20</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="28">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="28">
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
       <c r="L14" s="35">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
       <c r="N14" s="13"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
+      <c r="O14" s="55"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
       <c r="Y14" s="35">
         <f>P14+Q14+R14+S14+U14+V14+W14</f>
         <v>0</v>
@@ -26700,32 +26585,32 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <f t="shared" ref="C15" si="7">SUM(C8:C14)</f>
-        <v>602</v>
+        <f t="shared" ref="C15" si="6">SUM(C8:C14)</f>
+        <v>0</v>
       </c>
       <c r="D15" s="14">
         <f>D14/20</f>
         <v>0</v>
       </c>
       <c r="E15" s="14">
-        <f t="shared" ref="E15:J15" si="8">E14/20</f>
+        <f t="shared" ref="E15:J15" si="7">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K15" s="14"/>
@@ -26734,7 +26619,7 @@
         <v>22</v>
       </c>
       <c r="P15" s="14">
-        <f t="shared" ref="P15" si="9">SUM(P8:P14)</f>
+        <f t="shared" ref="P15" si="8">SUM(P8:P14)</f>
         <v>0</v>
       </c>
       <c r="Q15" s="14">
@@ -26742,24 +26627,24 @@
         <v>0</v>
       </c>
       <c r="R15" s="14">
-        <f t="shared" ref="R15:S15" si="10">R14/20</f>
+        <f t="shared" ref="R15:S15" si="9">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T15" s="14"/>
       <c r="U15" s="14">
-        <f t="shared" ref="U15:W15" si="11">U14/20</f>
+        <f t="shared" ref="U15:W15" si="10">U14/20</f>
         <v>0</v>
       </c>
       <c r="V15" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="W15" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X15" s="14"/>
@@ -26771,31 +26656,31 @@
       </c>
       <c r="C16" s="13">
         <f>C15+C14</f>
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" ref="D16:J16" si="12">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="11">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K16" s="13"/>
@@ -26808,28 +26693,28 @@
         <v>0</v>
       </c>
       <c r="Q16" s="13">
-        <f t="shared" ref="Q16:S16" si="13">Q15+Q14</f>
+        <f t="shared" ref="Q16:S16" si="12">Q15+Q14</f>
         <v>0</v>
       </c>
       <c r="R16" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T16" s="13"/>
       <c r="U16" s="13">
-        <f t="shared" ref="U16:W16" si="14">U15+U14</f>
+        <f t="shared" ref="U16:W16" si="13">U15+U14</f>
         <v>0</v>
       </c>
       <c r="V16" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="W16" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X16" s="13"/>
@@ -26875,35 +26760,35 @@
       <c r="B18" s="1"/>
       <c r="C18" s="41"/>
       <c r="D18" s="26">
-        <f t="shared" ref="D18:K18" si="15">D15/40</f>
+        <f t="shared" ref="D18:K18" si="14">D15/40</f>
         <v>0</v>
       </c>
       <c r="E18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K18" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -26981,103 +26866,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -27085,35 +26970,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -27207,18 +27092,18 @@
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="28">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="28">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M8" s="44"/>
       <c r="N8" s="27">
         <v>46179</v>
       </c>
@@ -27251,46 +27136,79 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="12">
+        <v>110</v>
+      </c>
+      <c r="D9" s="12">
+        <v>82</v>
+      </c>
+      <c r="E9" s="12">
+        <v>26</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
       <c r="G9" s="28">
-        <v>12</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+        <v>10.9</v>
+      </c>
+      <c r="H9" s="12">
+        <v>60</v>
+      </c>
+      <c r="I9" s="12">
+        <v>25</v>
+      </c>
+      <c r="J9" s="12">
+        <v>65</v>
+      </c>
       <c r="K9" s="28">
-        <v>33</v>
+        <v>8.0449999999999999</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="M9" s="44">
+        <v>8</v>
       </c>
       <c r="N9" s="27">
         <v>46179</v>
       </c>
       <c r="O9" s="10" t="str">
-        <f t="shared" ref="O9:O12" si="1">B9</f>
+        <f t="shared" ref="O9:O12" si="0">B9</f>
         <v>Salman</v>
       </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="P9" s="12">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>42</v>
+      </c>
+      <c r="R9" s="12">
+        <v>16</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
       <c r="T9" s="28">
         <v>12</v>
       </c>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
+      <c r="U9" s="12">
+        <v>40</v>
+      </c>
+      <c r="V9" s="12">
+        <v>25</v>
+      </c>
+      <c r="W9" s="12">
+        <v>45</v>
+      </c>
       <c r="X9" s="28">
         <v>33</v>
       </c>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="2">SUM(P9:S9,U9,V9,W9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="Y9:Y12" si="1">SUM(P9:S9,U9,V9,W9)/40</f>
+        <v>5.7</v>
+      </c>
+      <c r="Z9" s="70">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
@@ -27298,44 +27216,77 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="C10" s="12">
+        <v>200</v>
+      </c>
+      <c r="D10" s="12">
+        <v>40</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
       <c r="G10" s="28">
         <v>12</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
+      <c r="H10" s="12">
+        <v>130</v>
+      </c>
+      <c r="I10" s="12">
+        <v>50</v>
+      </c>
+      <c r="J10" s="12">
+        <v>260</v>
+      </c>
       <c r="K10" s="28">
-        <v>33</v>
+        <v>22.6</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="M10" s="44">
+        <v>10</v>
       </c>
       <c r="N10" s="27"/>
       <c r="O10" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Zesahn</v>
       </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="P10" s="12">
+        <v>200</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>40</v>
+      </c>
+      <c r="R10" s="12">
+        <v>0</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="28">
         <v>12</v>
       </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
+      <c r="U10" s="12">
+        <v>130</v>
+      </c>
+      <c r="V10" s="12">
+        <v>50</v>
+      </c>
+      <c r="W10" s="12">
+        <v>260</v>
+      </c>
       <c r="X10" s="28">
         <v>33</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="Z10" s="70">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
@@ -27343,44 +27294,75 @@
       <c r="B11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="C11" s="12">
+        <v>280</v>
+      </c>
+      <c r="D11" s="12">
+        <v>180</v>
+      </c>
+      <c r="E11" s="12">
+        <v>140</v>
+      </c>
       <c r="F11" s="12"/>
       <c r="G11" s="28">
-        <v>12</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="12">
+        <v>135</v>
+      </c>
+      <c r="I11" s="12">
+        <v>135</v>
+      </c>
+      <c r="J11" s="12">
+        <v>170</v>
+      </c>
       <c r="K11" s="28">
-        <v>33</v>
+        <v>23.5</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="M11" s="44">
+        <v>7</v>
       </c>
       <c r="N11" s="10"/>
       <c r="O11" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Umair</v>
       </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+      <c r="P11" s="12">
+        <v>140</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>180</v>
+      </c>
+      <c r="R11" s="12">
+        <v>140</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
       <c r="T11" s="28">
         <v>12</v>
       </c>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
+      <c r="U11" s="12">
+        <v>135</v>
+      </c>
+      <c r="V11" s="12">
+        <v>135</v>
+      </c>
+      <c r="W11" s="12">
+        <v>170</v>
+      </c>
       <c r="X11" s="28">
         <v>33</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="Z11" s="70">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
@@ -27388,44 +27370,75 @@
       <c r="B12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="C12" s="12">
+        <v>12</v>
+      </c>
+      <c r="D12" s="12">
+        <v>32</v>
+      </c>
+      <c r="E12" s="12">
+        <v>32</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
       <c r="G12" s="28">
-        <v>12</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="H12" s="12">
+        <v>110</v>
+      </c>
+      <c r="I12" s="12">
+        <v>85</v>
+      </c>
+      <c r="J12" s="12">
+        <v>85</v>
+      </c>
       <c r="K12" s="28">
-        <v>33</v>
+        <v>14.190000000000001</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.9</v>
+      </c>
+      <c r="M12" s="41">
+        <v>5</v>
       </c>
       <c r="N12" s="10"/>
       <c r="O12" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Mubeen</v>
       </c>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0</v>
+      </c>
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
       <c r="T12" s="28">
         <v>12</v>
       </c>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
+      <c r="U12" s="12">
+        <v>80</v>
+      </c>
+      <c r="V12" s="12">
+        <v>60</v>
+      </c>
+      <c r="W12" s="12">
+        <v>60</v>
+      </c>
       <c r="X12" s="28">
         <v>33</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Z12" s="70">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
@@ -27503,24 +27516,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="36">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="36"/>
       <c r="H15" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="36"/>
@@ -27534,24 +27547,24 @@
         <v>0</v>
       </c>
       <c r="R15" s="36">
-        <f t="shared" ref="R15:S15" si="4">R14/20</f>
+        <f t="shared" ref="R15:S15" si="3">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T15" s="36"/>
       <c r="U15" s="36">
-        <f t="shared" ref="U15:W15" si="5">U14/20</f>
+        <f t="shared" ref="U15:W15" si="4">U14/20</f>
         <v>0</v>
       </c>
       <c r="V15" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W15" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X15" s="36"/>
@@ -27566,28 +27579,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:J16" si="6">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="36"/>
       <c r="H16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K16" s="36"/>
@@ -27600,28 +27613,28 @@
         <v>0</v>
       </c>
       <c r="Q16" s="36">
-        <f t="shared" ref="Q16:S16" si="7">Q15+Q14</f>
+        <f t="shared" ref="Q16:S16" si="6">Q15+Q14</f>
         <v>0</v>
       </c>
       <c r="R16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T16" s="36"/>
       <c r="U16" s="36">
-        <f t="shared" ref="U16:W16" si="8">U15+U14</f>
+        <f t="shared" ref="U16:W16" si="7">U15+U14</f>
         <v>0</v>
       </c>
       <c r="V16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X16" s="36"/>
@@ -27726,103 +27739,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -27830,35 +27843,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -27879,7 +27892,7 @@
       <c r="F7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="56" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="12" t="s">
@@ -27891,7 +27904,7 @@
       <c r="J7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="56" t="s">
         <v>8</v>
       </c>
       <c r="L7" s="12" t="s">
@@ -27945,33 +27958,53 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
+      <c r="C8" s="12">
+        <v>82</v>
+      </c>
+      <c r="D8" s="12">
+        <v>13</v>
+      </c>
+      <c r="E8" s="12">
+        <v>13</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="56">
+        <v>12</v>
+      </c>
+      <c r="H8" s="12">
+        <v>14</v>
+      </c>
+      <c r="I8" s="12">
+        <v>20</v>
+      </c>
+      <c r="J8" s="12">
+        <v>16</v>
+      </c>
+      <c r="K8" s="56">
+        <v>33</v>
+      </c>
       <c r="L8">
-        <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
+        <v>3.95</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
       </c>
       <c r="N8" s="27"/>
       <c r="O8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
       <c r="Y8">
         <f>SUM(P8:S8,U8,V8,W8)/40</f>
         <v>0</v>
@@ -27982,35 +28015,55 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
+      <c r="C9" s="12">
+        <v>80</v>
+      </c>
+      <c r="D9" s="12">
+        <v>80</v>
+      </c>
+      <c r="E9" s="12">
+        <v>80</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="56">
+        <v>12</v>
+      </c>
+      <c r="H9" s="12">
+        <v>80</v>
+      </c>
+      <c r="I9" s="12">
+        <v>60</v>
+      </c>
+      <c r="J9" s="12">
+        <v>60</v>
+      </c>
+      <c r="K9" s="56">
+        <v>33</v>
+      </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
       </c>
       <c r="N9" s="27"/>
       <c r="O9" s="10" t="str">
-        <f t="shared" ref="O9:O12" si="1">B9</f>
+        <f t="shared" ref="O9:O12" si="0">B9</f>
         <v>Salman</v>
       </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
       <c r="Y9">
-        <f t="shared" ref="Y9:Y12" si="2">SUM(P9:S9,U9,V9,W9)/40</f>
+        <f t="shared" ref="Y9:Y12" si="1">SUM(P9:S9,U9,V9,W9)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -28019,35 +28072,55 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
+      <c r="C10" s="12">
+        <v>40</v>
+      </c>
+      <c r="D10" s="12">
+        <v>20</v>
+      </c>
+      <c r="E10" s="12">
+        <v>20</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="56">
+        <v>12</v>
+      </c>
+      <c r="H10" s="12">
+        <v>95</v>
+      </c>
+      <c r="I10" s="12">
+        <v>50</v>
+      </c>
+      <c r="J10" s="12">
+        <v>95</v>
+      </c>
+      <c r="K10" s="56">
+        <v>33</v>
+      </c>
       <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
       </c>
       <c r="N10" s="27"/>
       <c r="O10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Zesahn</v>
+      </c>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10">
         <f t="shared" si="1"/>
-        <v>Zesahn</v>
-      </c>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -28056,35 +28129,55 @@
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
+      <c r="C11" s="12">
+        <v>242</v>
+      </c>
+      <c r="D11" s="12">
+        <v>52</v>
+      </c>
+      <c r="E11" s="12">
+        <v>52</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="56">
+        <v>12</v>
+      </c>
+      <c r="H11" s="12">
+        <v>15</v>
+      </c>
+      <c r="I11" s="12">
+        <v>10</v>
+      </c>
+      <c r="J11" s="12">
+        <v>15</v>
+      </c>
+      <c r="K11" s="56">
+        <v>33</v>
+      </c>
       <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.65</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
       </c>
       <c r="N11" s="11"/>
       <c r="O11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Umair</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11">
         <f t="shared" si="1"/>
-        <v>Umair</v>
-      </c>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -28093,35 +28186,55 @@
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
+      <c r="C12" s="12">
+        <v>20</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="56">
+        <v>12</v>
+      </c>
+      <c r="H12" s="12">
+        <v>150</v>
+      </c>
+      <c r="I12" s="12">
+        <v>100</v>
+      </c>
+      <c r="J12" s="12">
+        <v>250</v>
+      </c>
+      <c r="K12" s="56">
+        <v>33</v>
+      </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="M12">
+        <v>8</v>
       </c>
       <c r="N12" s="11"/>
       <c r="O12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Mubeen</v>
+      </c>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12">
         <f t="shared" si="1"/>
-        <v>Mubeen</v>
-      </c>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -28132,102 +28245,102 @@
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="29"/>
+      <c r="G13" s="56"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
-      <c r="K13" s="29"/>
+      <c r="K13" s="56"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
-      <c r="T13" s="29"/>
+      <c r="T13" s="12"/>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
-      <c r="X13" s="29"/>
+      <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <v>464</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>165</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>165</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="33">
+        <f t="shared" si="2"/>
+        <v>60</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>354</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>240</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>436</v>
+      </c>
+      <c r="K14" s="33">
+        <f t="shared" si="2"/>
+        <v>165</v>
       </c>
       <c r="L14" s="35">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
+        <v>1824</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="10"/>
       <c r="P14" s="14">
-        <f t="shared" ref="P14:X14" si="4">SUM(P8:P13)</f>
+        <f t="shared" ref="P14:X14" si="3">SUM(P8:P13)</f>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y14" s="35">
@@ -28243,30 +28356,30 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>8.25</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="57"/>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>17.7</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>12</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="13"/>
+        <f t="shared" si="4"/>
+        <v>21.8</v>
+      </c>
+      <c r="K15" s="57"/>
       <c r="N15" s="13"/>
       <c r="O15" s="10" t="s">
         <v>22</v>
@@ -28277,24 +28390,24 @@
         <v>0</v>
       </c>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:S15" si="6">R14/20</f>
+        <f t="shared" ref="R15:S15" si="5">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T15" s="13"/>
       <c r="U15" s="13">
-        <f t="shared" ref="U15:W15" si="7">U14/20</f>
+        <f t="shared" ref="U15:W15" si="6">U14/20</f>
         <v>0</v>
       </c>
       <c r="V15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X15" s="13"/>
@@ -28306,34 +28419,34 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:J16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="7">D15+D14</f>
+        <v>173.25</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>173.25</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="33"/>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>371.7</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>252</v>
       </c>
       <c r="J16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="36"/>
+        <f t="shared" si="7"/>
+        <v>457.8</v>
+      </c>
+      <c r="K16" s="33"/>
       <c r="N16" s="13"/>
       <c r="O16" s="10" t="s">
         <v>21</v>
@@ -28343,28 +28456,28 @@
         <v>0</v>
       </c>
       <c r="Q16" s="36">
-        <f t="shared" ref="Q16:S16" si="9">Q15+Q14</f>
+        <f t="shared" ref="Q16:S16" si="8">Q15+Q14</f>
         <v>0</v>
       </c>
       <c r="R16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T16" s="36"/>
       <c r="U16" s="36">
-        <f t="shared" ref="U16:W16" si="10">U15+U14</f>
+        <f t="shared" ref="U16:W16" si="9">U15+U14</f>
         <v>0</v>
       </c>
       <c r="V16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X16" s="36"/>
@@ -28376,37 +28489,37 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:J17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="10">D14/40</f>
+        <v>4.125</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>4.125</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="33"/>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>8.85</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="J17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="36"/>
+        <f t="shared" si="10"/>
+        <v>10.9</v>
+      </c>
+      <c r="K17" s="33"/>
       <c r="L17" s="35">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>45.6</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="39" t="s">
@@ -28417,28 +28530,28 @@
         <v>0</v>
       </c>
       <c r="Q17" s="36">
-        <f t="shared" ref="Q17:S17" si="12">Q14/40</f>
+        <f t="shared" ref="Q17:S17" si="11">Q14/40</f>
         <v>0</v>
       </c>
       <c r="R17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T17" s="36"/>
       <c r="U17" s="36">
-        <f t="shared" ref="U17:W17" si="13">U14/40</f>
+        <f t="shared" ref="U17:W17" si="12">U14/40</f>
         <v>0</v>
       </c>
       <c r="V17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="W17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="X17" s="36"/>
@@ -28473,6 +28586,7 @@
     <mergeCell ref="U6:X6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28524,103 +28638,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="63"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
+      <c r="X4" s="63"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="63"/>
-      <c r="X5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -28628,35 +28742,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="66" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="66" t="s">
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="66"/>
-      <c r="W6" s="66"/>
-      <c r="X6" s="67"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAA5EF-CA47-40F9-BDA2-994B9F03BC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0E8FD7-73AE-49B3-B928-187396A69167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="8" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="9" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -630,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -799,6 +799,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1899,20 +1902,37 @@
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="C11" s="12">
+        <v>172</v>
+      </c>
+      <c r="D11" s="12">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12">
+        <v>20</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>148</v>
+      </c>
+      <c r="H11" s="12">
+        <v>208</v>
+      </c>
+      <c r="I11" s="12">
+        <v>284</v>
+      </c>
       <c r="J11" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
+        <v>21.3</v>
+      </c>
+      <c r="L11" s="71">
+        <v>11</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="10" t="str">
@@ -2020,15 +2040,15 @@
       </c>
       <c r="C14" s="14">
         <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
@@ -2036,23 +2056,23 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="J14" s="30">
         <f t="shared" ref="J14" si="4">SUM(G14:I14)/20</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="10" t="s">
@@ -2103,11 +2123,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="7">E14/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="7"/>
@@ -2115,15 +2135,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="J15" s="13"/>
       <c r="M15" s="13"/>
@@ -2161,15 +2181,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="10">D15+D14</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="10"/>
@@ -2177,15 +2197,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>155.4</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>218.4</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>298.2</v>
       </c>
       <c r="J16" s="36"/>
       <c r="M16" s="13"/>
@@ -2226,15 +2246,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="13">D14/40</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="13"/>
@@ -2242,20 +2262,20 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
+        <v>21.299999999999997</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="39" t="s">
@@ -27423,17 +27443,34 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
+      <c r="N10" s="12">
+        <v>40</v>
+      </c>
+      <c r="O10" s="12">
+        <v>90</v>
+      </c>
+      <c r="P10" s="12">
+        <v>130</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>115</v>
+      </c>
+      <c r="S10" s="12">
+        <v>10</v>
+      </c>
+      <c r="T10" s="12">
+        <v>75</v>
+      </c>
       <c r="U10" s="28"/>
       <c r="V10">
         <f>SUM(N10:Q10,R10,S10,T10)/40</f>
-        <v>0</v>
+        <v>11.5</v>
+      </c>
+      <c r="W10" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -27495,24 +27532,41 @@
         <v>12.35</v>
       </c>
       <c r="K12" s="41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Umair</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
+      <c r="N12" s="12">
+        <v>254</v>
+      </c>
+      <c r="O12" s="12">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <v>85</v>
+      </c>
+      <c r="S12" s="12">
+        <v>85</v>
+      </c>
+      <c r="T12" s="12">
+        <v>70</v>
+      </c>
       <c r="U12" s="28"/>
       <c r="V12">
         <f>SUM(N12:Q12,R12,S12,T12)/40</f>
-        <v>0</v>
+        <v>12.35</v>
+      </c>
+      <c r="W12" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
@@ -27575,15 +27629,15 @@
       <c r="M14" s="10"/>
       <c r="N14" s="14">
         <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
-        <v>132</v>
+        <v>426</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="2"/>
@@ -27591,15 +27645,15 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="2"/>
-        <v>97</v>
+        <v>297</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>201</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="2"/>
@@ -27607,7 +27661,7 @@
       </c>
       <c r="V14" s="35">
         <f>N14+O14+P14+Q14+R14+S14+T14</f>
-        <v>392</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.35">
@@ -27644,11 +27698,11 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15:Q15" si="4">P14/20</f>
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="13">
         <f t="shared" si="4"/>
@@ -27656,15 +27710,15 @@
       </c>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>4.8499999999999996</v>
+        <v>14.85</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>0.35</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="5"/>
-        <v>2.8</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="U15" s="13"/>
     </row>
@@ -27704,15 +27758,15 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>132</v>
+        <v>426</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:Q16" si="7">O15+O14</f>
-        <v>52.5</v>
+        <v>147</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="7"/>
-        <v>52.5</v>
+        <v>189</v>
       </c>
       <c r="Q16" s="36">
         <f t="shared" si="7"/>
@@ -27720,15 +27774,15 @@
       </c>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>101.85</v>
+        <v>311.85000000000002</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="8"/>
-        <v>7.35</v>
+        <v>107.1</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="8"/>
-        <v>58.8</v>
+        <v>211.05</v>
       </c>
       <c r="U16" s="36"/>
     </row>
@@ -27772,15 +27826,15 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>3.3</v>
+        <v>10.65</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:Q17" si="10">O14/40</f>
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="10"/>
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q17" s="36">
         <f t="shared" si="10"/>
@@ -27788,20 +27842,20 @@
       </c>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>2.4249999999999998</v>
+        <v>7.4249999999999998</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="11"/>
-        <v>0.17499999999999999</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="11"/>
-        <v>1.4</v>
+        <v>5.0250000000000004</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>9.8000000000000007</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0E8FD7-73AE-49B3-B928-187396A69167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3795BB-57D5-4D5B-8648-4C9E8C9EDD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="9" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -1770,20 +1770,37 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="C8" s="12">
+        <v>64</v>
+      </c>
+      <c r="D8" s="12">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>12</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>16</v>
+      </c>
+      <c r="H8" s="12">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12">
+        <v>16</v>
+      </c>
       <c r="J8" s="30">
         <f>SUM(G8:I8)/20</f>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
+        <v>3.4</v>
+      </c>
+      <c r="L8" s="71">
+        <v>4</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="10" t="str">
@@ -1814,20 +1831,37 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="C9" s="12">
+        <v>141</v>
+      </c>
+      <c r="D9" s="12">
+        <v>67</v>
+      </c>
+      <c r="E9" s="12">
+        <v>32</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>20</v>
+      </c>
+      <c r="H9" s="12">
+        <v>20</v>
+      </c>
+      <c r="I9" s="12">
+        <v>30</v>
+      </c>
       <c r="J9" s="30">
         <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
+        <v>7.75</v>
+      </c>
+      <c r="L9" s="44">
+        <v>7</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="10" t="str">
@@ -1858,20 +1892,37 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="C10" s="12">
+        <v>140</v>
+      </c>
+      <c r="D10" s="12">
+        <v>80</v>
+      </c>
+      <c r="E10" s="12">
+        <v>60</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>160</v>
+      </c>
+      <c r="H10" s="12">
+        <v>110</v>
+      </c>
+      <c r="I10" s="12">
+        <v>140</v>
+      </c>
       <c r="J10" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="K10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
+        <v>17.25</v>
+      </c>
+      <c r="L10" s="44">
+        <v>9</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="10" t="str">
@@ -1931,7 +1982,7 @@
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
         <v>21.3</v>
       </c>
-      <c r="L11" s="71">
+      <c r="L11" s="44">
         <v>11</v>
       </c>
       <c r="M11" s="11"/>
@@ -2040,15 +2091,15 @@
       </c>
       <c r="C14" s="14">
         <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
-        <v>172</v>
+        <v>517</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
@@ -2056,23 +2107,23 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>148</v>
+        <v>344</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>208</v>
+        <v>354</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>284</v>
+        <v>470</v>
       </c>
       <c r="J14" s="30">
         <f t="shared" ref="J14" si="4">SUM(G14:I14)/20</f>
-        <v>32</v>
+        <v>58.4</v>
       </c>
       <c r="K14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>852</v>
+        <v>1988</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="10" t="s">
@@ -2123,11 +2174,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>1</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="7">E14/20</f>
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="7"/>
@@ -2135,15 +2186,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="7"/>
-        <v>7.4</v>
+        <v>17.2</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="7"/>
-        <v>10.4</v>
+        <v>17.7</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="7"/>
-        <v>14.2</v>
+        <v>23.5</v>
       </c>
       <c r="J15" s="13"/>
       <c r="M15" s="13"/>
@@ -2181,15 +2232,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>172</v>
+        <v>517</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="10">D15+D14</f>
-        <v>21</v>
+        <v>187.95</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>130.19999999999999</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="10"/>
@@ -2197,15 +2248,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="10"/>
-        <v>155.4</v>
+        <v>361.2</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="10"/>
-        <v>218.4</v>
+        <v>371.7</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="10"/>
-        <v>298.2</v>
+        <v>493.5</v>
       </c>
       <c r="J16" s="36"/>
       <c r="M16" s="13"/>
@@ -2246,15 +2297,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>4.3</v>
+        <v>12.925000000000001</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="13">D14/40</f>
-        <v>0.5</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="13"/>
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="13"/>
@@ -2262,20 +2313,20 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="13"/>
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="13"/>
-        <v>5.2</v>
+        <v>8.85</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="13"/>
-        <v>7.1</v>
+        <v>11.75</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>21.299999999999997</v>
+        <v>49.7</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="39" t="s">

--- a/july 2026/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3795BB-57D5-4D5B-8648-4C9E8C9EDD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C41F88-0E42-4D4B-BA19-558696AB4EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="9" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="10" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="41">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -630,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -799,9 +799,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1744,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="R7" s="45" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S7" s="45" t="s">
         <v>13</v>
@@ -1756,7 +1753,7 @@
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>27</v>
@@ -1799,7 +1796,7 @@
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>3.4</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="44">
         <v>4</v>
       </c>
       <c r="M8" s="27"/>
@@ -1807,22 +1804,30 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
+      <c r="O8" s="12">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
       <c r="R8" s="30">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
       <c r="U8" s="12"/>
       <c r="V8" s="30">
-        <f>SUM(S8:U8)/20</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
+        <f>SUM(O8:V8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -1853,7 +1858,7 @@
         <v>30</v>
       </c>
       <c r="J9" s="30">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
+        <f t="shared" ref="J9:J13" si="0">SUM(G9:I9)/20</f>
         <v>3.5</v>
       </c>
       <c r="K9">
@@ -1868,23 +1873,34 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
+      <c r="O9" s="12">
+        <v>126</v>
+      </c>
+      <c r="P9" s="12">
+        <v>37</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>22</v>
+      </c>
       <c r="R9" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="12">
+        <v>20</v>
+      </c>
+      <c r="T9" s="12">
+        <v>20</v>
+      </c>
       <c r="U9" s="12"/>
       <c r="V9" s="30">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="W9:W12" si="1">SUM(O9:V9)/40</f>
+        <v>6.375</v>
+      </c>
+      <c r="X9" s="44">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
@@ -1914,7 +1930,7 @@
         <v>140</v>
       </c>
       <c r="J10" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
       <c r="K10">
@@ -1929,23 +1945,34 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
+      <c r="O10" s="12">
+        <v>90</v>
+      </c>
+      <c r="P10" s="12">
+        <v>60</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>40</v>
+      </c>
       <c r="R10" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="12">
+        <v>145</v>
+      </c>
+      <c r="T10" s="12">
+        <v>100</v>
+      </c>
       <c r="U10" s="12"/>
       <c r="V10" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>13.75</v>
+      </c>
+      <c r="X10" s="44">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
@@ -1975,7 +2002,7 @@
         <v>284</v>
       </c>
       <c r="J11" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="K11">
@@ -1990,23 +2017,34 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
+      <c r="O11" s="12">
+        <v>132</v>
+      </c>
+      <c r="P11" s="12">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>20</v>
+      </c>
       <c r="R11" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
+        <v>148</v>
+      </c>
+      <c r="T11" s="12">
+        <v>208</v>
+      </c>
       <c r="U11" s="12"/>
       <c r="V11" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>20.3</v>
+      </c>
+      <c r="X11" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
@@ -2022,7 +2060,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12">
@@ -2037,19 +2075,13 @@
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R12" s="30"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
-      <c r="V12" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="V12" s="30"/>
       <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2064,7 +2096,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M13" s="11"/>
@@ -2072,17 +2104,11 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-      <c r="R13" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R13" s="30"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
-      <c r="V13" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="V13" s="30"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
@@ -2090,35 +2116,35 @@
         <v>16</v>
       </c>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
         <v>517</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>124</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>344</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>354</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>470</v>
       </c>
       <c r="J14" s="30">
-        <f t="shared" ref="J14" si="4">SUM(G14:I14)/20</f>
+        <f t="shared" ref="J14" si="3">SUM(G14:I14)/20</f>
         <v>58.4</v>
       </c>
       <c r="K14" s="35">
@@ -2130,37 +2156,31 @@
         <v>16</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:U14" si="5">SUM(O8:O13)</f>
-        <v>0</v>
+        <f t="shared" ref="O14:U14" si="4">SUM(O8:O13)</f>
+        <v>348</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>117</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>82</v>
+      </c>
+      <c r="R14" s="31"/>
       <c r="S14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>313</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>328</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="30">
-        <f t="shared" ref="V14" si="6">SUM(S14:U14)/20</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="30"/>
       <c r="W14" s="35" t="e">
         <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
         <v>#REF!</v>
@@ -2177,23 +2197,23 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="7">E14/20</f>
+        <f t="shared" ref="E15:I15" si="5">E14/20</f>
         <v>6.2</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>17.2</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>17.7</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>23.5</v>
       </c>
       <c r="J15" s="13"/>
@@ -2204,23 +2224,23 @@
       <c r="O15" s="13"/>
       <c r="P15" s="13">
         <f>P14/20</f>
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="8">Q14/20</f>
-        <v>0</v>
+        <f t="shared" ref="Q15" si="6">Q14/20</f>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R15" s="13"/>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="9">S14/20</f>
-        <v>0</v>
+        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <v>15.65</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>16.399999999999999</v>
       </c>
       <c r="U15" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V15" s="13"/>
@@ -2235,27 +2255,27 @@
         <v>517</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="10">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
         <v>187.95</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>130.19999999999999</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>361.2</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>371.7</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>493.5</v>
       </c>
       <c r="J16" s="36"/>
@@ -2265,27 +2285,27 @@
       </c>
       <c r="O16" s="36">
         <f>O15+O14</f>
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="11">P15+P14</f>
-        <v>0</v>
+        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
+        <v>122.85</v>
       </c>
       <c r="Q16" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>86.1</v>
       </c>
       <c r="R16" s="36"/>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="12">S15+S14</f>
-        <v>0</v>
+        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
+        <v>328.65</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>344.4</v>
       </c>
       <c r="U16" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V16" s="36"/>
@@ -2300,27 +2320,27 @@
         <v>12.925000000000001</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="13">D14/40</f>
+        <f t="shared" ref="D17:I17" si="11">D14/40</f>
         <v>4.4749999999999996</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3.1</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>8.6</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>8.85</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>11.75</v>
       </c>
       <c r="J17" s="36"/>
@@ -2334,33 +2354,33 @@
       </c>
       <c r="O17" s="36">
         <f>O14/40</f>
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="14">P14/40</f>
-        <v>0</v>
+        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
+        <v>2.9249999999999998</v>
       </c>
       <c r="Q17" s="36">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>2.0499999999999998</v>
       </c>
       <c r="R17" s="36"/>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="15">S14/40</f>
-        <v>0</v>
+        <f t="shared" ref="S17:U17" si="13">S14/40</f>
+        <v>7.8250000000000002</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>8.1999999999999993</v>
       </c>
       <c r="U17" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="V17" s="36"/>
       <c r="W17" s="35">
         <f>SUM(O17:U17)</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
@@ -2393,7 +2413,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB8BBA6-E6CB-45EB-B741-EF1A3D434FE9}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -2404,16 +2424,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2423,7 +2442,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -2432,10 +2451,8 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="59" t="s">
         <v>36</v>
@@ -2447,21 +2464,19 @@
       <c r="G2" s="60"/>
       <c r="H2" s="60"/>
       <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="59" t="s">
         <v>37</v>
       </c>
+      <c r="N2" s="60"/>
       <c r="O2" s="60"/>
       <c r="P2" s="60"/>
       <c r="Q2" s="60"/>
       <c r="R2" s="60"/>
       <c r="S2" s="60"/>
       <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="62"/>
       <c r="C3" s="63"/>
@@ -2471,19 +2486,17 @@
       <c r="G3" s="63"/>
       <c r="H3" s="63"/>
       <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="63"/>
       <c r="O3" s="63"/>
       <c r="P3" s="63"/>
       <c r="Q3" s="63"/>
       <c r="R3" s="63"/>
       <c r="S3" s="63"/>
       <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="62"/>
       <c r="C4" s="63"/>
@@ -2493,19 +2506,17 @@
       <c r="G4" s="63"/>
       <c r="H4" s="63"/>
       <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="63"/>
       <c r="O4" s="63"/>
       <c r="P4" s="63"/>
       <c r="Q4" s="63"/>
       <c r="R4" s="63"/>
       <c r="S4" s="63"/>
       <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="65"/>
       <c r="C5" s="66"/>
@@ -2515,19 +2526,17 @@
       <c r="G5" s="66"/>
       <c r="H5" s="66"/>
       <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="66"/>
       <c r="O5" s="66"/>
       <c r="P5" s="66"/>
       <c r="Q5" s="66"/>
       <c r="R5" s="66"/>
       <c r="S5" s="66"/>
       <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -2543,25 +2552,23 @@
       </c>
       <c r="H6" s="69"/>
       <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="O6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="P6" s="69"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="69" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="69"/>
       <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -2590,52 +2597,46 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="V7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -2647,171 +2648,182 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="C9" s="12">
+        <v>72</v>
+      </c>
+      <c r="D9" s="12">
+        <v>104</v>
+      </c>
+      <c r="E9" s="12">
+        <v>30</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>58</v>
+      </c>
+      <c r="H9" s="12">
+        <v>34</v>
+      </c>
+      <c r="I9" s="12">
+        <v>50</v>
+      </c>
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K9" s="44">
+        <v>9</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>40</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" s="44">
+        <v>1</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="C11" s="12">
+        <v>210</v>
+      </c>
+      <c r="D11" s="12">
+        <v>40</v>
+      </c>
+      <c r="E11" s="12">
+        <v>40</v>
+      </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="G11" s="12">
+        <v>54</v>
+      </c>
+      <c r="H11" s="12">
+        <v>62</v>
+      </c>
+      <c r="I11" s="12">
+        <v>62</v>
+      </c>
+      <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>11.7</v>
+      </c>
+      <c r="K11" s="44">
+        <v>9</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -2823,39 +2835,31 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -2865,106 +2869,90 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>282</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>144</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>70</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>152</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>96</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>856</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -2972,199 +2960,193 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>3.5</v>
       </c>
       <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>7.6</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>5.6</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="T15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>151.19999999999999</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="6"/>
+        <v>73.5</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="6"/>
+        <v>159.6</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="6"/>
+        <v>100.8</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="6"/>
+        <v>117.6</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
+      <c r="T16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>3.6</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>1.75</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>3.8</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>2.4</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>2.8</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>21.4</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
+      <c r="T17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -3174,16 +3156,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:T5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:T6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
